--- a/handouts/chapter_2_2_handout.xlsx
+++ b/handouts/chapter_2_2_handout.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RussellStuff\Time series personal work\timeseries\handouts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\craigaj\Documents\GitHub\timeseries\handouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF692A4C-6DD9-496B-AEC0-A746C7ACC7DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503E0F48-A0A6-4B33-9609-9D326196E843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="9">
   <si>
     <t>sum</t>
   </si>
@@ -48,19 +48,10 @@
 </t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lag k=1, Sample Autocovariance Function, </t>
-  </si>
-  <si>
     <t>NA</t>
   </si>
   <si>
     <t>Lag k=2</t>
-  </si>
-  <si>
-    <t>____</t>
   </si>
   <si>
     <t>Na</t>
@@ -69,20 +60,17 @@
     <t>Lag k=3</t>
   </si>
   <si>
-    <t>Fill in the blanks in 'Lag k=2', Use the results to compute        and        .</t>
-  </si>
-  <si>
     <t>Lag k=4</t>
   </si>
   <si>
-    <t>Compute       and       using R (but not automated functions), Excel, or hand calculations.</t>
+    <t>Lag k=1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,73 +87,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.6"/>
-      <color rgb="FF000000"/>
-      <name val="Source Sans Pro"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.6"/>
-      <color rgb="FF56B4E9"/>
-      <name val="Source Sans Pro"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9.6"/>
-      <color rgb="FF009E73"/>
-      <name val="Source Sans Pro"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9.6"/>
-      <color rgb="FFF0E442"/>
-      <name val="Source Sans Pro"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9.6"/>
-      <color rgb="FF0072B2"/>
-      <name val="Source Sans Pro"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9.6"/>
-      <color rgb="FFD55E00"/>
-      <name val="Source Sans Pro"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9.6"/>
-      <color rgb="FFF5C710"/>
-      <name val="Source Sans Pro"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9.6"/>
-      <color rgb="FFCC79A7"/>
-      <name val="Source Sans Pro"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9.6"/>
-      <color rgb="FF999999"/>
-      <name val="Source Sans Pro"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9.6"/>
-      <color rgb="FFE69F00"/>
-      <name val="Source Sans Pro"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -173,8 +94,62 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF56B4E9"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF009E73"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFF0E442"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0072B2"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFD55E00"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFF5C710"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFCC79A7"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF999999"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFE69F00"/>
       <name val="Source Sans Pro"/>
       <family val="2"/>
     </font>
@@ -194,12 +169,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="3" tint="0.89999084444715716"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -246,102 +221,10 @@
         <color indexed="64"/>
       </right>
       <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFB3B3B3"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFB3B3B3"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFB3B3B3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -380,25 +263,12 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FFB3B3B3"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -408,8 +278,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FFB3B3B3"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -421,179 +291,97 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FFB3B3B3"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -722,10 +510,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -980,10 +765,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1134,10 +916,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1306,10 +1085,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1509,10 +1285,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1687,10 +1460,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1861,302 +1631,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>876300</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>163830</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="218201" cy="252826"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2" name="TextBox 1">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40CD72E9-924A-9422-A247-94A5312EF6A2}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4892040" y="163830"/>
-              <a:ext cx="218201" cy="252826"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1600" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1600" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑐</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1600" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>1</m:t>
-                        </m:r>
-                      </m:sub>
-                    </m:sSub>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1600"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2" name="TextBox 1">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40CD72E9-924A-9422-A247-94A5312EF6A2}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4892040" y="163830"/>
-              <a:ext cx="218201" cy="252826"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1600" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑐_1</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1600"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>53340</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>72390</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="318613" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DB6FB1F-8803-661B-8FB0-B6711650F3AB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="6377940" y="689610"/>
-              <a:ext cx="318613" cy="221214"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̅"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:accPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑥</m:t>
-                        </m:r>
-                      </m:e>
-                    </m:acc>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>=</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1400"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DB6FB1F-8803-661B-8FB0-B6711650F3AB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="6377940" y="689610"/>
-              <a:ext cx="318613" cy="221214"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1400" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑥 ̅=</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1400"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>318294</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>45593</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="196079" cy="221214"/>
@@ -2206,10 +1683,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -2304,12 +1778,12 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>257334</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>45593</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="367280" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">
@@ -2354,10 +1828,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -2397,7 +1868,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">
@@ -2458,7 +1929,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>89694</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>60833</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="510973" cy="221214"/>
@@ -2508,10 +1979,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -2630,7 +2098,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>89694</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>53213</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="663515" cy="225446"/>
@@ -2680,10 +2148,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -2833,12 +2298,12 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>143034</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>53213</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="682174" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -2883,10 +2348,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -2950,7 +2412,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -3011,12 +2473,12 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>59214</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>68453</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1316322" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -3061,10 +2523,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -3176,7 +2635,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -3287,10 +2746,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -3389,8 +2845,8 @@
       <xdr:rowOff>45593</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="367280" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="TextBox 15">
@@ -3435,10 +2891,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -3478,7 +2931,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="TextBox 15">
@@ -3589,10 +3042,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -3761,10 +3211,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -3918,8 +3365,8 @@
       <xdr:rowOff>53213</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="682174" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="28" name="TextBox 27">
@@ -3964,10 +3411,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -4031,7 +3475,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="28" name="TextBox 27">
@@ -4096,8 +3540,8 @@
       <xdr:rowOff>68453</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1316322" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="31" name="TextBox 30">
@@ -4142,10 +3586,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -4257,7 +3698,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="31" name="TextBox 30">
@@ -4316,304 +3757,10 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>678180</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="222946" cy="252826"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="33" name="TextBox 32">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{614FCCCA-6AA0-4DEE-848A-FF8184AFD0EB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3924300" y="3417570"/>
-              <a:ext cx="222946" cy="252826"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1600" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1600" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑐</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1600" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>2</m:t>
-                        </m:r>
-                      </m:sub>
-                    </m:sSub>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1600"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="33" name="TextBox 32">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{614FCCCA-6AA0-4DEE-848A-FF8184AFD0EB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3924300" y="3417570"/>
-              <a:ext cx="222946" cy="252826"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1600" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑐_2</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1600"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>403860</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="208583" cy="252826"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="34" name="TextBox 33">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C615A30B-8205-404F-BB09-AD907FDBBE38}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4419600" y="3409950"/>
-              <a:ext cx="208583" cy="252826"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1600" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1600" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑟</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1600" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>2</m:t>
-                        </m:r>
-                      </m:sub>
-                    </m:sSub>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1600"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="34" name="TextBox 33">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C615A30B-8205-404F-BB09-AD907FDBBE38}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4419600" y="3409950"/>
-              <a:ext cx="208583" cy="252826"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1600" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_2</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1600"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:colOff>423545</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="324961" cy="189604"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -4631,7 +3778,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6438900" y="6903720"/>
+              <a:off x="6856095" y="8919210"/>
               <a:ext cx="324961" cy="189604"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4662,14 +3809,11 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1200" i="1">
+                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -4719,7 +3863,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6438900" y="6903720"/>
+              <a:off x="6856095" y="8919210"/>
               <a:ext cx="324961" cy="189604"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4747,6 +3891,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1200" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -4764,9 +3909,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>339090</xdr:rowOff>
+      <xdr:colOff>428931</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>2540</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="314189" cy="189604"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -4784,7 +3929,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6339840" y="7181850"/>
+              <a:off x="6861481" y="9127490"/>
               <a:ext cx="314189" cy="189604"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4815,14 +3960,11 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1200" i="1">
+                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -4872,7 +4014,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6339840" y="7181850"/>
+              <a:off x="6861481" y="9127490"/>
               <a:ext cx="314189" cy="189604"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4900,6 +4042,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1200" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -4918,7 +4061,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>318294</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>45593</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="196079" cy="221214"/>
@@ -4968,10 +4111,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -5066,12 +4206,12 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>264954</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>45593</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="367280" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="38" name="TextBox 37">
@@ -5116,10 +4256,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -5159,7 +4296,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="38" name="TextBox 37">
@@ -5220,7 +4357,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>89694</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>60833</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="510973" cy="221214"/>
@@ -5270,10 +4407,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -5392,7 +4526,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>89694</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>53213</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="663515" cy="225446"/>
@@ -5442,10 +4576,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -5595,12 +4726,12 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>143034</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>53213</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="682174" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="41" name="TextBox 40">
@@ -5645,10 +4776,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -5712,7 +4840,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="41" name="TextBox 40">
@@ -5773,12 +4901,12 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>59214</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>68453</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1316322" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="42" name="TextBox 41">
@@ -5823,10 +4951,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -5938,7 +5063,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="42" name="TextBox 41">
@@ -5997,304 +5122,10 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>213360</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="167225" cy="189604"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="43" name="TextBox 42">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7C03CE8-DC2E-46C6-AEB8-2662D9C2E2AB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="1028700" y="9471660"/>
-              <a:ext cx="167225" cy="189604"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1200" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑐</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>4</m:t>
-                        </m:r>
-                      </m:sub>
-                    </m:sSub>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1200"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="43" name="TextBox 42">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7C03CE8-DC2E-46C6-AEB8-2662D9C2E2AB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="1028700" y="9471660"/>
-              <a:ext cx="167225" cy="189604"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑐_4</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1200"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="149849" cy="189604"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="44" name="TextBox 43">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3D7435A-0FBD-44A8-83AD-2AF45588F6F5}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="1501140" y="9479280"/>
-              <a:ext cx="149849" cy="189604"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1200" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑟</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>4</m:t>
-                        </m:r>
-                      </m:sub>
-                    </m:sSub>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1200"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="44" name="TextBox 43">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3D7435A-0FBD-44A8-83AD-2AF45588F6F5}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="1501140" y="9479280"/>
-              <a:ext cx="149849" cy="189604"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_4</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1200"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:colOff>423545</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>156210</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="324961" cy="189604"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -6312,7 +5143,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6438900" y="4000500"/>
+              <a:off x="6856095" y="5991860"/>
               <a:ext cx="324961" cy="189604"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6343,14 +5174,11 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1200" i="1">
+                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -6400,7 +5228,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6438900" y="4000500"/>
+              <a:off x="6856095" y="5991860"/>
               <a:ext cx="324961" cy="189604"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6428,6 +5256,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1200" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -6445,9 +5274,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>339090</xdr:rowOff>
+      <xdr:colOff>428931</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>186690</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="314189" cy="189604"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -6465,7 +5294,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6339840" y="4278630"/>
+              <a:off x="6861481" y="6212840"/>
               <a:ext cx="314189" cy="189604"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6496,14 +5325,11 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1200" i="1">
+                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -6553,7 +5379,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6339840" y="4278630"/>
+              <a:off x="6861481" y="6212840"/>
               <a:ext cx="314189" cy="189604"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6581,6 +5407,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1200" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -6598,9 +5425,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:colOff>423545</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>156210</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="324961" cy="189604"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -6618,7 +5445,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6438900" y="10195560"/>
+              <a:off x="6856095" y="12195810"/>
               <a:ext cx="324961" cy="189604"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6649,14 +5476,11 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1200" i="1">
+                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -6706,7 +5530,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6438900" y="10195560"/>
+              <a:off x="6856095" y="12195810"/>
               <a:ext cx="324961" cy="189604"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6734,6 +5558,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1200" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -6751,9 +5576,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>339090</xdr:rowOff>
+      <xdr:colOff>432233</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>180340</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="307585" cy="189604"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -6771,7 +5596,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6339840" y="10473690"/>
+              <a:off x="6864783" y="12410440"/>
               <a:ext cx="307585" cy="189604"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6802,14 +5627,11 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1200" i="1">
+                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -6859,7 +5681,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6339840" y="10473690"/>
+              <a:off x="6864783" y="12410440"/>
               <a:ext cx="307585" cy="189604"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6887,6 +5709,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1200" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -6894,6 +5717,603 @@
                 <a:t>𝑟_4=</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1200" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>423545</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>168910</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="324961" cy="189604"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="54" name="TextBox 53">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85563DC8-6C4C-48F7-91CB-4CA9023F23FA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6856095" y="1343660"/>
+              <a:ext cx="324961" cy="189604"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑐</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>0</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" sz="1200"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="54" name="TextBox 53">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85563DC8-6C4C-48F7-91CB-4CA9023F23FA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6856095" y="1343660"/>
+              <a:ext cx="324961" cy="189604"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑐_0=</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1200"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>425340</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>187960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="321370" cy="189604"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="55" name="TextBox 54">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FBEF375-D87F-42C1-9F2D-89308F670421}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6857890" y="2696210"/>
+              <a:ext cx="321370" cy="189604"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑐</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>1</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" sz="1200"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="55" name="TextBox 54">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FBEF375-D87F-42C1-9F2D-89308F670421}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6857890" y="2696210"/>
+              <a:ext cx="321370" cy="189604"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑐_1=</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1200"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>430726</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>168910</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="310598" cy="189604"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="56" name="TextBox 55">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87446C54-34B9-49AA-A96B-761FD98505CD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6863276" y="2867660"/>
+              <a:ext cx="310598" cy="189604"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑟</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>1</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" sz="1200"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="56" name="TextBox 55">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87446C54-34B9-49AA-A96B-761FD98505CD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6863276" y="2867660"/>
+              <a:ext cx="310598" cy="189604"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑟_1=</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1200"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>449482</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>359410</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="273087" cy="189604"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="57" name="TextBox 56">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06908424-916D-4DD2-8CA1-E01A36E4C321}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6882032" y="975360"/>
+              <a:ext cx="273087" cy="189604"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:acc>
+                      <m:accPr>
+                        <m:chr m:val="̅"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:accPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1200" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑥</m:t>
+                        </m:r>
+                      </m:e>
+                    </m:acc>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" sz="1200"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="57" name="TextBox 56">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06908424-916D-4DD2-8CA1-E01A36E4C321}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6882032" y="975360"/>
+              <a:ext cx="273087" cy="189604"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑥 ̅=</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1200"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -7221,7 +6641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ABFF2E6-1E13-48EF-9BE3-D6C90C46BEC8}">
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.90625" customWidth="1"/>
@@ -7234,36 +6654,32 @@
     <col min="13" max="13" width="9.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="48.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="35" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="37"/>
+    <row r="1" spans="1:9" s="22" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="25"/>
     </row>
-    <row r="2" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="20">
-        <f>AVERAGE(B3:B12)</f>
-        <v>4.7</v>
-      </c>
     </row>
-    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="15">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
         <v>1</v>
       </c>
       <c r="B3" s="5">
@@ -7273,26 +6689,27 @@
         <v>4.2</v>
       </c>
       <c r="D3" s="4">
-        <v>-0.3</v>
+        <v>-0.29999999999999982</v>
       </c>
       <c r="E3" s="4">
-        <v>0.09</v>
+        <v>8.99999999999999E-2</v>
       </c>
       <c r="F3" s="4">
         <v>-0.5</v>
       </c>
-      <c r="G3" s="16">
-        <v>0.15</v>
-      </c>
+      <c r="G3" s="4">
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="I3" s="7"/>
     </row>
-    <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="15">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
         <v>2</v>
       </c>
       <c r="B4" s="6">
         <v>4.2</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="8">
         <v>4.2</v>
       </c>
       <c r="D4" s="4">
@@ -7304,18 +6721,18 @@
       <c r="F4" s="4">
         <v>-0.5</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="4">
         <v>0.25</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="15">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
         <v>3</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="8">
         <v>4.2</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="9">
         <v>4</v>
       </c>
       <c r="D5" s="4">
@@ -7325,66 +6742,67 @@
         <v>0.25</v>
       </c>
       <c r="F5" s="4">
-        <v>-0.7</v>
-      </c>
-      <c r="G5" s="16">
-        <v>0.35</v>
-      </c>
+        <v>-0.70000000000000018</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.35000000000000009</v>
+      </c>
+      <c r="I5" s="7"/>
     </row>
-    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="15">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="9">
         <v>4</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="D6" s="4">
-        <v>-0.7</v>
+        <v>-0.70000000000000018</v>
       </c>
       <c r="E6" s="4">
-        <v>0.49</v>
+        <v>0.49000000000000027</v>
       </c>
       <c r="F6" s="4">
-        <v>-0.3</v>
-      </c>
-      <c r="G6" s="16">
-        <v>0.21</v>
+        <v>-0.29999999999999982</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0.20999999999999994</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="15">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
         <v>5</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="11">
         <v>4.7</v>
       </c>
       <c r="D7" s="4">
-        <v>-0.3</v>
+        <v>-0.29999999999999982</v>
       </c>
       <c r="E7" s="4">
-        <v>0.09</v>
+        <v>8.99999999999999E-2</v>
       </c>
       <c r="F7" s="4">
         <v>0</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="15">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
         <v>6</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="11">
         <v>4.7</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="12">
         <v>4.9000000000000004</v>
       </c>
       <c r="D8" s="4">
@@ -7394,196 +6812,208 @@
         <v>0</v>
       </c>
       <c r="F8" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="G8" s="16">
+        <v>0.20000000000000018</v>
+      </c>
+      <c r="G8" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="15">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
         <v>7</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="12">
         <v>4.9000000000000004</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="13">
         <v>5.3</v>
       </c>
       <c r="D9" s="4">
-        <v>0.2</v>
+        <v>0.20000000000000018</v>
       </c>
       <c r="E9" s="4">
-        <v>0.04</v>
+        <v>4.000000000000007E-2</v>
       </c>
       <c r="F9" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="G9" s="16">
-        <v>0.12</v>
+        <v>0.59999999999999964</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0.12000000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="15">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
         <v>8</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="13">
         <v>5.3</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="14">
         <v>5.4</v>
       </c>
       <c r="D10" s="4">
-        <v>0.6</v>
+        <v>0.59999999999999964</v>
       </c>
       <c r="E10" s="4">
-        <v>0.36</v>
+        <v>0.3599999999999996</v>
       </c>
       <c r="F10" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="G10" s="16">
-        <v>0.42</v>
+        <v>0.70000000000000018</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.41999999999999987</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="15">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
         <v>9</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="14">
         <v>5.4</v>
       </c>
       <c r="C11" s="5">
         <v>5.5</v>
       </c>
       <c r="D11" s="4">
-        <v>0.7</v>
+        <v>0.70000000000000018</v>
       </c>
       <c r="E11" s="4">
-        <v>0.49</v>
+        <v>0.49000000000000027</v>
       </c>
       <c r="F11" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="G11" s="16">
+        <v>0.79999999999999982</v>
+      </c>
+      <c r="G11" s="4">
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="15">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
         <v>10</v>
       </c>
       <c r="B12" s="5">
         <v>5.5</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" s="4">
-        <v>0.8</v>
+        <v>0.79999999999999982</v>
       </c>
       <c r="E12" s="4">
-        <v>0.64</v>
+        <v>0.63999999999999968</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="7"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="17" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="16">
         <v>47</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="16">
         <v>42.6</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="16">
         <v>0</v>
       </c>
-      <c r="E13" s="18">
-        <v>2.7</v>
-      </c>
-      <c r="F13" s="18">
-        <v>0.3</v>
-      </c>
-      <c r="G13" s="19">
+      <c r="E13" s="16">
+        <v>2.6999999999999997</v>
+      </c>
+      <c r="F13" s="16">
+        <v>0.29999999999999982</v>
+      </c>
+      <c r="G13" s="17">
         <v>2.06</v>
       </c>
+      <c r="I13" s="7"/>
     </row>
-    <row r="15" spans="1:8" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
+    <row r="16" spans="1:9" s="22" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="25"/>
     </row>
-    <row r="17" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A17" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="36"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="37"/>
+    <row r="17" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
     </row>
-    <row r="18" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="21" t="s">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
         <v>1</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="5">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C18" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="D18" s="4">
+        <v>-0.3</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0.09</v>
+      </c>
+      <c r="F18" s="4">
+        <v>-0.5</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
         <v>2</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="I18" s="50"/>
+      <c r="B19" s="6">
+        <v>4.2</v>
+      </c>
+      <c r="C19" s="9">
+        <v>4</v>
+      </c>
+      <c r="D19" s="4">
+        <v>-0.5</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="F19" s="4">
+        <v>-0.7</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0.35</v>
+      </c>
     </row>
-    <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="24">
-        <v>1</v>
-      </c>
-      <c r="B19" s="25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>3</v>
+      </c>
+      <c r="B20" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="C20" s="10">
         <v>4.4000000000000004</v>
-      </c>
-      <c r="C19" s="25">
-        <v>4.2</v>
-      </c>
-      <c r="D19" s="25">
-        <v>-0.3</v>
-      </c>
-      <c r="E19" s="25">
-        <v>0.09</v>
-      </c>
-      <c r="F19" s="25">
-        <v>-0.5</v>
-      </c>
-      <c r="G19" s="26">
-        <v>0.15</v>
-      </c>
-      <c r="I19" s="50"/>
-    </row>
-    <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="15">
-        <v>2</v>
-      </c>
-      <c r="B20" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="C20" s="4">
-        <v>4</v>
       </c>
       <c r="D20" s="4">
         <v>-0.5</v>
@@ -7592,254 +7022,206 @@
         <v>0.25</v>
       </c>
       <c r="F20" s="4">
+        <v>-0.3</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
+        <v>4</v>
+      </c>
+      <c r="B21" s="9">
+        <v>4</v>
+      </c>
+      <c r="C21" s="26"/>
+      <c r="D21" s="4">
         <v>-0.7</v>
       </c>
-      <c r="G20" s="16">
-        <v>0.35</v>
-      </c>
+      <c r="E21" s="4">
+        <v>0.49</v>
+      </c>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
     </row>
-    <row r="21" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="15">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="4">
+        <v>5</v>
+      </c>
+      <c r="B22" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C22" s="26"/>
+      <c r="D22" s="4">
+        <v>-0.3</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0.09</v>
+      </c>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>6</v>
+      </c>
+      <c r="B23" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="C23" s="26"/>
+      <c r="D23" s="4">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>7</v>
+      </c>
+      <c r="B24" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="C24" s="14">
+        <v>5.4</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="E24" s="4">
+        <v>0.04</v>
+      </c>
+      <c r="F24" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="G24" s="4">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>8</v>
+      </c>
+      <c r="B25" s="13">
+        <v>5.3</v>
+      </c>
+      <c r="C25" s="5">
+        <v>5.5</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0.36</v>
+      </c>
+      <c r="F25" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="G25" s="4">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="4">
+        <v>9</v>
+      </c>
+      <c r="B26" s="14">
+        <v>5.4</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="C21" s="39">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="D21" s="39">
-        <v>-0.5</v>
-      </c>
-      <c r="E21" s="39">
-        <v>0.25</v>
-      </c>
-      <c r="F21" s="39">
-        <v>-0.3</v>
-      </c>
-      <c r="G21" s="40">
-        <v>0.15</v>
+      <c r="D26" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="E26" s="4">
+        <v>0.49</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="15">
-        <v>4</v>
-      </c>
-      <c r="B22" s="4">
-        <v>4</v>
-      </c>
-      <c r="C22" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="G22" s="41" t="s">
-        <v>7</v>
-      </c>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
+        <v>10</v>
+      </c>
+      <c r="B27" s="5">
+        <v>5.5</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="E27" s="4">
+        <v>0.64</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="7"/>
     </row>
-    <row r="23" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="15">
-        <v>5</v>
-      </c>
-      <c r="B23" s="4">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C23" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="G23" s="41" t="s">
-        <v>7</v>
-      </c>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="19">
+        <v>47</v>
+      </c>
+      <c r="C28" s="27"/>
+      <c r="D28" s="19">
+        <v>0</v>
+      </c>
+      <c r="E28" s="19">
+        <v>2.7</v>
+      </c>
+      <c r="F28" s="27"/>
+      <c r="G28" s="28"/>
+      <c r="I28" s="7"/>
     </row>
-    <row r="24" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="15">
+    <row r="31" spans="1:9" s="22" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B24" s="4">
-        <v>4.7</v>
-      </c>
-      <c r="C24" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="G24" s="41" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="15">
-        <v>7</v>
-      </c>
-      <c r="B25" s="4">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="C25" s="4">
-        <v>5.4</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="E25" s="4">
-        <v>0.04</v>
-      </c>
-      <c r="F25" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="G25" s="16">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="15">
-        <v>8</v>
-      </c>
-      <c r="B26" s="4">
-        <v>5.3</v>
-      </c>
-      <c r="C26" s="4">
-        <v>5.5</v>
-      </c>
-      <c r="D26" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="E26" s="4">
-        <v>0.36</v>
-      </c>
-      <c r="F26" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="G26" s="16">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="15">
-        <v>9</v>
-      </c>
-      <c r="B27" s="4">
-        <v>5.4</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="E27" s="4">
-        <v>0.49</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G27" s="16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="15">
-        <v>10</v>
-      </c>
-      <c r="B28" s="4">
-        <v>5.5</v>
-      </c>
-      <c r="C28" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="39">
-        <v>0.8</v>
-      </c>
-      <c r="E28" s="39">
-        <v>0.64</v>
-      </c>
-      <c r="F28" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="G28" s="40" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" s="18">
-        <v>47</v>
-      </c>
-      <c r="C29" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="G29" s="41" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A31" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="32"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="33"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="25"/>
     </row>
     <row r="32" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32">
-        <v>0.02</v>
-      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
     </row>
-    <row r="33" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
         <v>1</v>
       </c>
       <c r="B33" s="5">
         <v>4.4000000000000004</v>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="9">
         <v>4</v>
       </c>
       <c r="D33" s="4">
@@ -7851,21 +7233,18 @@
       <c r="F33" s="4">
         <v>-0.7</v>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="4">
         <v>0.21</v>
       </c>
-      <c r="H33">
-        <v>7.4099999999999999E-2</v>
-      </c>
     </row>
-    <row r="34" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="4">
         <v>2</v>
       </c>
       <c r="B34" s="6">
         <v>4.2</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="D34" s="4">
@@ -7877,18 +7256,18 @@
       <c r="F34" s="4">
         <v>-0.3</v>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="4">
         <v>0.15</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="4">
         <v>3</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="8">
         <v>4.2</v>
       </c>
-      <c r="C35" s="10">
+      <c r="C35" s="11">
         <v>4.7</v>
       </c>
       <c r="D35" s="4">
@@ -7900,18 +7279,18 @@
       <c r="F35" s="4">
         <v>0</v>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="4">
         <v>4</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="9">
         <v>4</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="12">
         <v>4.9000000000000004</v>
       </c>
       <c r="D36" s="4">
@@ -7923,18 +7302,18 @@
       <c r="F36" s="4">
         <v>0.2</v>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="4">
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="4">
         <v>5</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B37" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="13">
         <v>5.3</v>
       </c>
       <c r="D37" s="4">
@@ -7946,18 +7325,18 @@
       <c r="F37" s="4">
         <v>0.6</v>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="4">
         <v>-0.18</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="4">
         <v>6</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="11">
         <v>4.7</v>
       </c>
-      <c r="C38" s="13">
+      <c r="C38" s="14">
         <v>5.4</v>
       </c>
       <c r="D38" s="4">
@@ -7969,18 +7348,18 @@
       <c r="F38" s="4">
         <v>0.7</v>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="4">
         <v>7</v>
       </c>
-      <c r="B39" s="11">
+      <c r="B39" s="12">
         <v>4.9000000000000004</v>
       </c>
-      <c r="C39" s="49">
+      <c r="C39" s="5">
         <v>5.5</v>
       </c>
       <c r="D39" s="4">
@@ -7989,293 +7368,264 @@
       <c r="E39" s="4">
         <v>0.04</v>
       </c>
-      <c r="F39" s="39">
+      <c r="F39" s="4">
         <v>0.8</v>
       </c>
-      <c r="G39" s="40">
+      <c r="G39" s="4">
         <v>0.16</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="4">
         <v>8</v>
       </c>
-      <c r="B40" s="12">
+      <c r="B40" s="13">
         <v>5.3</v>
       </c>
-      <c r="C40" s="41" t="s">
-        <v>3</v>
-      </c>
+      <c r="C40" s="26"/>
       <c r="D40" s="4">
         <v>0.6</v>
       </c>
       <c r="E40" s="4">
         <v>0.36</v>
       </c>
-      <c r="F40" s="41" t="s">
-        <v>3</v>
-      </c>
-      <c r="G40" s="41" t="s">
-        <v>3</v>
-      </c>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
     </row>
-    <row r="41" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="4">
         <v>9</v>
       </c>
-      <c r="B41" s="13">
+      <c r="B41" s="14">
         <v>5.4</v>
       </c>
-      <c r="C41" s="41" t="s">
-        <v>3</v>
-      </c>
+      <c r="C41" s="26"/>
       <c r="D41" s="4">
         <v>0.7</v>
       </c>
       <c r="E41" s="4">
         <v>0.49</v>
       </c>
-      <c r="F41" s="41" t="s">
-        <v>3</v>
-      </c>
-      <c r="G41" s="41" t="s">
-        <v>3</v>
-      </c>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
     </row>
-    <row r="42" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="4">
         <v>10</v>
       </c>
       <c r="B42" s="5">
         <v>5.5</v>
       </c>
-      <c r="C42" s="41" t="s">
-        <v>3</v>
-      </c>
+      <c r="C42" s="26"/>
       <c r="D42" s="4">
         <v>0.8</v>
       </c>
       <c r="E42" s="4">
         <v>0.64</v>
       </c>
-      <c r="F42" s="41" t="s">
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="I42" s="7"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="16">
+        <v>47</v>
+      </c>
+      <c r="C43" s="16">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="D43" s="16">
+        <v>0</v>
+      </c>
+      <c r="E43" s="16">
+        <v>2.7</v>
+      </c>
+      <c r="F43" s="16">
+        <v>1.3</v>
+      </c>
+      <c r="G43" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="I43" s="7"/>
+    </row>
+    <row r="46" spans="1:9" s="22" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="24"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="25"/>
+    </row>
+    <row r="47" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48" s="4">
+        <v>1</v>
+      </c>
+      <c r="B48" s="5">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="26"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49" s="4">
+        <v>2</v>
+      </c>
+      <c r="B49" s="6">
+        <v>4.2</v>
+      </c>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50" s="4">
         <v>3</v>
       </c>
-      <c r="G42" s="41" t="s">
-        <v>3</v>
-      </c>
+      <c r="B50" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="C50" s="26"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="26"/>
+      <c r="G50" s="26"/>
     </row>
-    <row r="43" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="14" t="s">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51" s="4">
+        <v>4</v>
+      </c>
+      <c r="B51" s="9">
+        <v>4</v>
+      </c>
+      <c r="C51" s="26"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="26"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52" s="4">
+        <v>5</v>
+      </c>
+      <c r="B52" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C52" s="26"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="26"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53" s="4">
+        <v>6</v>
+      </c>
+      <c r="B53" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="C53" s="26"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+      <c r="G53" s="26"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54" s="4">
+        <v>7</v>
+      </c>
+      <c r="B54" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55" s="4">
+        <v>8</v>
+      </c>
+      <c r="B55" s="13">
+        <v>5.3</v>
+      </c>
+      <c r="C55" s="26"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="26"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56" s="4">
+        <v>9</v>
+      </c>
+      <c r="B56" s="14">
+        <v>5.4</v>
+      </c>
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57" s="4">
+        <v>10</v>
+      </c>
+      <c r="B57" s="5">
+        <v>5.5</v>
+      </c>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
+      <c r="I57" s="7"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B43" s="14">
+      <c r="B58" s="16">
         <v>47</v>
       </c>
-      <c r="C43" s="14">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="D43" s="14">
-        <v>0</v>
-      </c>
-      <c r="E43" s="14">
-        <v>2.7</v>
-      </c>
-      <c r="F43" s="14">
-        <v>1.3</v>
-      </c>
-      <c r="G43" s="30">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="B45" s="34"/>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="34"/>
-      <c r="F45" s="34"/>
-      <c r="G45" s="34"/>
-    </row>
-    <row r="47" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A47" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="B47" s="32"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="33"/>
-    </row>
-    <row r="48" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A48" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="B48" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="27"/>
-      <c r="D48" s="27"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="I48" s="50"/>
-    </row>
-    <row r="49" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="4">
-        <v>1</v>
-      </c>
-      <c r="B49" s="5">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C49" s="42"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="I49" s="50"/>
-    </row>
-    <row r="50" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="4">
-        <v>2</v>
-      </c>
-      <c r="B50" s="6">
-        <v>4.2</v>
-      </c>
-      <c r="C50" s="43"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="41"/>
-    </row>
-    <row r="51" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="4">
-        <v>3</v>
-      </c>
-      <c r="B51" s="7">
-        <v>4.2</v>
-      </c>
-      <c r="C51" s="44"/>
-      <c r="D51" s="41"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="41"/>
-      <c r="G51" s="41"/>
-    </row>
-    <row r="52" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="4">
-        <v>4</v>
-      </c>
-      <c r="B52" s="8">
-        <v>4</v>
-      </c>
-      <c r="C52" s="45"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
-    </row>
-    <row r="53" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="4">
-        <v>5</v>
-      </c>
-      <c r="B53" s="9">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C53" s="46"/>
-      <c r="D53" s="41"/>
-      <c r="E53" s="41"/>
-      <c r="F53" s="41"/>
-      <c r="G53" s="41"/>
-    </row>
-    <row r="54" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="4">
-        <v>6</v>
-      </c>
-      <c r="B54" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="C54" s="47"/>
-      <c r="D54" s="41"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="41"/>
-    </row>
-    <row r="55" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="4">
-        <v>7</v>
-      </c>
-      <c r="B55" s="11">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="C55" s="48"/>
-      <c r="D55" s="41"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="41"/>
-      <c r="G55" s="41"/>
-    </row>
-    <row r="56" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="4">
-        <v>8</v>
-      </c>
-      <c r="B56" s="12">
-        <v>5.3</v>
-      </c>
-      <c r="C56" s="41"/>
-      <c r="D56" s="41"/>
-      <c r="E56" s="41"/>
-      <c r="F56" s="41"/>
-      <c r="G56" s="41"/>
-    </row>
-    <row r="57" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="4">
-        <v>9</v>
-      </c>
-      <c r="B57" s="13">
-        <v>5.4</v>
-      </c>
-      <c r="C57" s="41"/>
-      <c r="D57" s="41"/>
-      <c r="E57" s="41"/>
-      <c r="F57" s="41"/>
-      <c r="G57" s="41"/>
-    </row>
-    <row r="58" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="4">
-        <v>10</v>
-      </c>
-      <c r="B58" s="5">
-        <v>5.5</v>
-      </c>
-      <c r="C58" s="41"/>
-      <c r="D58" s="41"/>
-      <c r="E58" s="41"/>
-      <c r="F58" s="41"/>
-      <c r="G58" s="41"/>
-    </row>
-    <row r="59" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B59" s="14">
-        <v>47</v>
-      </c>
-      <c r="C59" s="41"/>
-      <c r="D59" s="41"/>
-      <c r="E59" s="41"/>
-      <c r="F59" s="41"/>
-      <c r="G59" s="41"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="21"/>
+      <c r="I58" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A47:G47"/>
-    <mergeCell ref="A45:G45"/>
+  <mergeCells count="4">
+    <mergeCell ref="A46:G46"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A15:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8292,15 +7642,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010070F75838E79B0E48B83E8E3F5479A3A2" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2b0c304636f8f537543cd13f583db9d4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xmlns:ns4="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f089f22c5ce4e61126931f7622145b2" ns3:_="" ns4:_="">
     <xsd:import namespace="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
@@ -8495,6 +7836,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E1B631-90B0-4D19-A35E-F8DC8BE167A4}">
   <ds:schemaRefs>
@@ -8513,14 +7863,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBDDC771-C014-4A48-9FCA-802C556EA1D0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8537,4 +7879,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/handouts/chapter_2_2_handout.xlsx
+++ b/handouts/chapter_2_2_handout.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\craigaj\Documents\GitHub\timeseries\handouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503E0F48-A0A6-4B33-9609-9D326196E843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A94151F9-1C8C-41BB-942B-57399B9900FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
   </bookViews>
@@ -364,6 +364,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -372,15 +381,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6655,15 +6655,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="22" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="25"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="28"/>
     </row>
     <row r="2" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -6936,15 +6936,15 @@
       <c r="I13" s="7"/>
     </row>
     <row r="16" spans="1:9" s="22" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="25"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="28"/>
     </row>
     <row r="17" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
@@ -7035,15 +7035,15 @@
       <c r="B21" s="9">
         <v>4</v>
       </c>
-      <c r="C21" s="26"/>
+      <c r="C21" s="23"/>
       <c r="D21" s="4">
         <v>-0.7</v>
       </c>
       <c r="E21" s="4">
         <v>0.49</v>
       </c>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
@@ -7052,15 +7052,15 @@
       <c r="B22" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="C22" s="26"/>
+      <c r="C22" s="23"/>
       <c r="D22" s="4">
         <v>-0.3</v>
       </c>
       <c r="E22" s="4">
         <v>0.09</v>
       </c>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
@@ -7069,15 +7069,15 @@
       <c r="B23" s="11">
         <v>4.7</v>
       </c>
-      <c r="C23" s="26"/>
+      <c r="C23" s="23"/>
       <c r="D23" s="4">
         <v>0</v>
       </c>
       <c r="E23" s="4">
         <v>0</v>
       </c>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
@@ -7179,27 +7179,27 @@
       <c r="B28" s="19">
         <v>47</v>
       </c>
-      <c r="C28" s="27"/>
+      <c r="C28" s="24"/>
       <c r="D28" s="19">
         <v>0</v>
       </c>
       <c r="E28" s="19">
         <v>2.7</v>
       </c>
-      <c r="F28" s="27"/>
-      <c r="G28" s="28"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="25"/>
       <c r="I28" s="7"/>
     </row>
     <row r="31" spans="1:9" s="22" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="24"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="25"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="28"/>
     </row>
     <row r="32" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
@@ -7382,15 +7382,15 @@
       <c r="B40" s="13">
         <v>5.3</v>
       </c>
-      <c r="C40" s="26"/>
+      <c r="C40" s="23"/>
       <c r="D40" s="4">
         <v>0.6</v>
       </c>
       <c r="E40" s="4">
         <v>0.36</v>
       </c>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="4">
@@ -7399,15 +7399,15 @@
       <c r="B41" s="14">
         <v>5.4</v>
       </c>
-      <c r="C41" s="26"/>
+      <c r="C41" s="23"/>
       <c r="D41" s="4">
         <v>0.7</v>
       </c>
       <c r="E41" s="4">
         <v>0.49</v>
       </c>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="4">
@@ -7416,15 +7416,15 @@
       <c r="B42" s="5">
         <v>5.5</v>
       </c>
-      <c r="C42" s="26"/>
+      <c r="C42" s="23"/>
       <c r="D42" s="4">
         <v>0.8</v>
       </c>
       <c r="E42" s="4">
         <v>0.64</v>
       </c>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
       <c r="I42" s="7"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
@@ -7452,15 +7452,15 @@
       <c r="I43" s="7"/>
     </row>
     <row r="46" spans="1:9" s="22" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="23" t="s">
+      <c r="A46" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B46" s="24"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="25"/>
+      <c r="B46" s="27"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="28"/>
     </row>
     <row r="47" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
@@ -7482,11 +7482,11 @@
       <c r="B48" s="5">
         <v>4.4000000000000004</v>
       </c>
-      <c r="C48" s="26"/>
-      <c r="D48" s="26"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="26"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="23"/>
+      <c r="F48" s="23"/>
+      <c r="G48" s="23"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="4">
@@ -7495,11 +7495,11 @@
       <c r="B49" s="6">
         <v>4.2</v>
       </c>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="26"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="23"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="4">
@@ -7508,11 +7508,11 @@
       <c r="B50" s="8">
         <v>4.2</v>
       </c>
-      <c r="C50" s="26"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="26"/>
-      <c r="G50" s="26"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="4">
@@ -7521,11 +7521,11 @@
       <c r="B51" s="9">
         <v>4</v>
       </c>
-      <c r="C51" s="26"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="26"/>
-      <c r="F51" s="26"/>
-      <c r="G51" s="26"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="23"/>
+      <c r="F51" s="23"/>
+      <c r="G51" s="23"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="4">
@@ -7534,11 +7534,11 @@
       <c r="B52" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="C52" s="26"/>
-      <c r="D52" s="26"/>
-      <c r="E52" s="26"/>
-      <c r="F52" s="26"/>
-      <c r="G52" s="26"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="4">
@@ -7547,11 +7547,11 @@
       <c r="B53" s="11">
         <v>4.7</v>
       </c>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="26"/>
+      <c r="C53" s="23"/>
+      <c r="D53" s="23"/>
+      <c r="E53" s="23"/>
+      <c r="F53" s="23"/>
+      <c r="G53" s="23"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="4">
@@ -7560,11 +7560,11 @@
       <c r="B54" s="12">
         <v>4.9000000000000004</v>
       </c>
-      <c r="C54" s="26"/>
-      <c r="D54" s="26"/>
-      <c r="E54" s="26"/>
-      <c r="F54" s="26"/>
-      <c r="G54" s="26"/>
+      <c r="C54" s="23"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="23"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="23"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="4">
@@ -7573,11 +7573,11 @@
       <c r="B55" s="13">
         <v>5.3</v>
       </c>
-      <c r="C55" s="26"/>
-      <c r="D55" s="26"/>
-      <c r="E55" s="26"/>
-      <c r="F55" s="26"/>
-      <c r="G55" s="26"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="23"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="4">
@@ -7586,11 +7586,11 @@
       <c r="B56" s="14">
         <v>5.4</v>
       </c>
-      <c r="C56" s="26"/>
-      <c r="D56" s="26"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="26"/>
-      <c r="G56" s="26"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="23"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="4">
@@ -7599,11 +7599,11 @@
       <c r="B57" s="5">
         <v>5.5</v>
       </c>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="26"/>
-      <c r="G57" s="26"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="23"/>
+      <c r="F57" s="23"/>
+      <c r="G57" s="23"/>
       <c r="I57" s="7"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
@@ -7642,6 +7642,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010070F75838E79B0E48B83E8E3F5479A3A2" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2b0c304636f8f537543cd13f583db9d4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xmlns:ns4="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f089f22c5ce4e61126931f7622145b2" ns3:_="" ns4:_="">
     <xsd:import namespace="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
@@ -7836,15 +7845,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E1B631-90B0-4D19-A35E-F8DC8BE167A4}">
   <ds:schemaRefs>
@@ -7863,6 +7863,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBDDC771-C014-4A48-9FCA-802C556EA1D0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7879,12 +7887,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>